--- a/data/employees/EMP073/AST-EMP073-06.xlsx
+++ b/data/employees/EMP073/AST-EMP073-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment Inventory Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Equipment Inventory Tracker - Taylor Miller (Manufacturing)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Taylor Miller | Role: Architect | Location: Fremont | Date: 2025-03-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>76</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>83</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Line ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>OEE %</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Downtime (min)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Units Produced</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Defect Rate %</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>91</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L-01</t>
+          <t>EMP073</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CNC Mill A</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="D5" t="n">
-        <v>12</v>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>4200</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.8</v>
+        <v>86</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L-02</t>
+          <t>EMP073</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Assembly Arm B</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>91</v>
-      </c>
-      <c r="D6" t="n">
-        <v>5</v>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>5100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.3</v>
+        <v>73</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L-03</t>
+          <t>EMP073</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Conveyor Unit C</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>45</v>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>3800</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.2</v>
+        <v>71</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L-04</t>
+          <t>EMP073</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Laser Cutter D</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.1</v>
+        <v>93</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>61</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>92</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>69</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>77</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>75</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>68</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>70</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>94</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>91</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>93</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>64</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>68</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>79</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>97</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>60</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>65</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp073 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>76</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP073</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP073 contributes to ast emp073 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>